--- a/Results/Methanol/methanol climate change image breakdown results.xlsx
+++ b/Results/Methanol/methanol climate change image breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7637053688642204</v>
+        <v>0.7637053688642201</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1867935009068545</v>
+        <v>0.1867935009068543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4923714659308644</v>
+        <v>0.4923714659308646</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05200835814725648</v>
+        <v>0.05200835814725645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001067732353612944</v>
+        <v>0.0001067732353612939</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000162820804278003</v>
+        <v>0.0001628208042780026</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005286314349593295</v>
+        <v>0.0005286314349593282</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004139107301173977</v>
+        <v>0.0004139107301173978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000431815991783113</v>
+        <v>0.0004318159917828688</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003589945926490617</v>
+        <v>0.0003589945926490613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001423100974447725</v>
+        <v>0.001423100974447686</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599611564901</v>
+        <v>0.02910599611564924</v>
       </c>
     </row>
     <row r="3">
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7587127580564578</v>
+        <v>0.7587127580564583</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853863416547733</v>
+        <v>0.1853863416547732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4910773732529224</v>
+        <v>0.4910773732529227</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04986741037531088</v>
+        <v>0.04986741037531069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001020728379294522</v>
+        <v>0.0001020728379294524</v>
       </c>
       <c r="I3" t="n">
         <v>0.0001543848552269669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005033555848161305</v>
+        <v>0.0005033555848161309</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004035815179113713</v>
+        <v>0.0004035815179113719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004154471741204062</v>
+        <v>0.0004154471741203773</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003528653539079975</v>
+        <v>0.0003528653539079979</v>
       </c>
       <c r="N3" t="n">
         <v>0.001343929378793109</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599607074571</v>
+        <v>0.02910599607074627</v>
       </c>
     </row>
     <row r="4">
@@ -620,37 +620,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7555157706438181</v>
+        <v>0.7555157706438176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1843045463719579</v>
+        <v>0.1843045463719576</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4902065091285822</v>
+        <v>0.490206509128582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04878455486382748</v>
+        <v>0.04878455486382769</v>
       </c>
       <c r="H4" t="n">
-        <v>9.927352951629169e-05</v>
+        <v>9.927352951629176e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001491813170349933</v>
+        <v>0.0001491813170349978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004840237189151271</v>
+        <v>0.0004840237189151329</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003907306092057178</v>
+        <v>0.0003907306092057171</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004068474043469856</v>
+        <v>0.0004068474043467823</v>
       </c>
       <c r="M4" t="n">
         <v>0.000346111908938109</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001237995751058907</v>
+        <v>0.001237995751058908</v>
       </c>
       <c r="O4" t="n">
         <v>0.02910599604043451</v>
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7498826282037706</v>
+        <v>0.7498826282037715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1832303534811839</v>
+        <v>0.183230353481184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4890894138049241</v>
+        <v>0.4890894138049242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04546793851780918</v>
+        <v>0.04546793851780911</v>
       </c>
       <c r="H5" t="n">
-        <v>9.433295702090309e-05</v>
+        <v>9.433295702090335e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001425295224211094</v>
+        <v>0.0001425295224211093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004638043232824564</v>
+        <v>0.0004638043232824572</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003839268978225562</v>
+        <v>0.0003839268978225555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003957260291865897</v>
+        <v>0.0003957260291872756</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003398823232683074</v>
+        <v>0.000339882323268307</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001168724359204892</v>
+        <v>0.001168724359204894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599598764663</v>
+        <v>0.02910599598764674</v>
       </c>
     </row>
     <row r="6">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7023771077035208</v>
+        <v>0.7023771077035205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1742114073783753</v>
+        <v>0.1742114073783752</v>
       </c>
       <c r="F6" t="n">
         <v>0.4818322848993405</v>
@@ -734,28 +734,28 @@
         <v>0.01512053462978461</v>
       </c>
       <c r="H6" t="n">
-        <v>4.627778588802687e-05</v>
+        <v>4.627778588802682e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.427256342897692e-05</v>
+        <v>8.427256342897677e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002727500360475493</v>
+        <v>0.0002727500360475498</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000333125007998954</v>
+        <v>0.0003331250079989536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002619602979930308</v>
+        <v>0.0002619602979925605</v>
       </c>
       <c r="M6" t="n">
         <v>0.0003004277448122441</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008080719002817884</v>
+        <v>0.0008080719002817896</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599545956993</v>
+        <v>0.02910599545957004</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.668583677578219</v>
+        <v>0.6685836775782195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1670001535399246</v>
+        <v>0.1670001535399248</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4760736555836547</v>
+        <v>0.4760736555836552</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.004937697265714205</v>
+        <v>-0.004937697265714171</v>
       </c>
       <c r="H7" t="n">
-        <v>1.121067028185039e-05</v>
+        <v>1.12106702818505e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.928231993952035e-05</v>
+        <v>3.928231993952055e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001179691972618888</v>
+        <v>0.0001179691972618887</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002831740359223623</v>
+        <v>0.0002831740359223611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001696270356181512</v>
+        <v>0.0001696270356176103</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002698716403295495</v>
+        <v>0.0002698716403295494</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004504357304151712</v>
+        <v>0.0004504357304151745</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599509058553</v>
+        <v>0.02910599509058576</v>
       </c>
     </row>
     <row r="8">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6610223730866212</v>
+        <v>0.6610223730866218</v>
       </c>
       <c r="E8" t="n">
-        <v>0.165035449895415</v>
+        <v>0.1650354498954149</v>
       </c>
       <c r="F8" t="n">
         <v>0.4744042824202051</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008676015011131997</v>
+        <v>-0.008676015011131983</v>
       </c>
       <c r="H8" t="n">
-        <v>3.56239416742364e-06</v>
+        <v>3.562394167423636e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.183983614280515e-05</v>
+        <v>3.183983614280502e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.560562487960585e-05</v>
+        <v>8.560562487960501e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002684537004831268</v>
+        <v>0.0002684537004831265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001495133400146371</v>
+        <v>0.0001495133400148695</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002632184485004548</v>
+        <v>0.0002632184485004554</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003504674230908818</v>
+        <v>0.0003504674230908813</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599501485411</v>
+        <v>0.02910599501485467</v>
       </c>
     </row>
     <row r="9">
@@ -878,37 +878,37 @@
         <v>0.7440488351015296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1822659711988444</v>
+        <v>0.1822659711988445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4883924985936149</v>
+        <v>0.4883924985936147</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04134214626745768</v>
+        <v>0.04134214626745761</v>
       </c>
       <c r="H9" t="n">
-        <v>8.798208131902881e-05</v>
+        <v>8.798208131902848e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000138014185136545</v>
+        <v>0.0001380141851365453</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004426989295353248</v>
+        <v>0.0004426989295353267</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000379624658811963</v>
+        <v>0.0003796246588119625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003754309712545094</v>
+        <v>0.0003754309712549646</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003427765497631473</v>
+        <v>0.0003427765497631437</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001175695747841813</v>
+        <v>0.001175695747841808</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599591795038</v>
+        <v>0.02910599591795004</v>
       </c>
     </row>
     <row r="10">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6994606648437901</v>
+        <v>0.6994606648437897</v>
       </c>
       <c r="E10" t="n">
         <v>0.1735186361978786</v>
@@ -935,31 +935,31 @@
         <v>0.4812722470351943</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01355015218311554</v>
+        <v>0.01355015218311549</v>
       </c>
       <c r="H10" t="n">
-        <v>4.281361698979363e-05</v>
+        <v>4.281361698979369e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>8.42909451062986e-05</v>
+        <v>8.429094510629887e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002471518015613615</v>
+        <v>0.000247151801561361</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003291111247146678</v>
+        <v>0.0003291111247146677</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002534848688862133</v>
+        <v>0.0002534848688861409</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003092144791355733</v>
+        <v>0.0003092144791355738</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007475671624110944</v>
+        <v>0.0007475671624110939</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599542879666</v>
+        <v>0.02910599542879633</v>
       </c>
     </row>
     <row r="11">
@@ -977,40 +977,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6726614526308752</v>
+        <v>0.6726614526308744</v>
       </c>
       <c r="E11" t="n">
         <v>0.1682601739045025</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4774368746780103</v>
+        <v>0.47743687467801</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.003602093331550962</v>
+        <v>-0.003602093331551</v>
       </c>
       <c r="H11" t="n">
-        <v>1.561661817671832e-05</v>
+        <v>1.561661817671804e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>4.624225401687235e-05</v>
+        <v>4.624225401687266e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001379871920300388</v>
+        <v>0.0001379871920300356</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002943872889499769</v>
+        <v>0.0002943872889499766</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001800216207149133</v>
+        <v>0.0001800216207148012</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002740818955873554</v>
+        <v>0.0002740818955873534</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005121653923314337</v>
+        <v>0.0005121653923313846</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910599511810597</v>
+        <v>0.02910599511810585</v>
       </c>
     </row>
   </sheetData>
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4767783229955008</v>
+        <v>0.4767783229955003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1867935009068545</v>
+        <v>0.1867935009068543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2054444129547421</v>
+        <v>0.2054444129547423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05200835814725648</v>
+        <v>0.05200835814725645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001067732353612944</v>
+        <v>0.0001067732353612939</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000162820804278003</v>
+        <v>0.0001628208042780026</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005286314349593295</v>
+        <v>0.0005286314349593282</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004139107301173977</v>
+        <v>0.0004139107301173978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000431815991783113</v>
+        <v>0.0004318159917828688</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003589945926490617</v>
+        <v>0.0003589945926490613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001423100974447725</v>
+        <v>0.001423100974447686</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600322305185</v>
+        <v>0.02910600322305168</v>
       </c>
     </row>
     <row r="3">
@@ -1165,40 +1165,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4682190584950329</v>
+        <v>0.4682190584950326</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853863416547733</v>
+        <v>0.1853863416547732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2005836664957465</v>
+        <v>0.2005836664957467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04986741037531088</v>
+        <v>0.04986741037531069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001020728379294522</v>
+        <v>0.0001020728379294524</v>
       </c>
       <c r="I3" t="n">
         <v>0.0001543848552269669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005033555848161305</v>
+        <v>0.0005033555848161309</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004035815179113713</v>
+        <v>0.0004035815179113719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004154471741204062</v>
+        <v>0.0004154471741203773</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003528653539079975</v>
+        <v>0.0003528653539079979</v>
       </c>
       <c r="N3" t="n">
         <v>0.001343929378793109</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600326649676</v>
+        <v>0.02910600326649665</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4632709816289229</v>
+        <v>0.4632709816289223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1843045463719579</v>
+        <v>0.1843045463719576</v>
       </c>
       <c r="F4" t="n">
         <v>0.1979617128745608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04878455486382748</v>
+        <v>0.04878455486382769</v>
       </c>
       <c r="H4" t="n">
-        <v>9.927352951629169e-05</v>
+        <v>9.927352951629176e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001491813170349933</v>
+        <v>0.0001491813170349978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004840237189151271</v>
+        <v>0.0004840237189151329</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003907306092057178</v>
+        <v>0.0003907306092057171</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004068474043469856</v>
+        <v>0.0004068474043467823</v>
       </c>
       <c r="M4" t="n">
         <v>0.000346111908938109</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001237995751058907</v>
+        <v>0.001237995751058908</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600327956059</v>
+        <v>0.02910600327956026</v>
       </c>
     </row>
     <row r="5">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4515718821068009</v>
+        <v>0.4515718821068008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1832303534811839</v>
+        <v>0.183230353481184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1907786603185696</v>
+        <v>0.1907786603185699</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04546793851780918</v>
+        <v>0.04546793851780911</v>
       </c>
       <c r="H5" t="n">
-        <v>9.433295702090309e-05</v>
+        <v>9.433295702090335e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001425295224211094</v>
+        <v>0.0001425295224211093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004638043232824564</v>
+        <v>0.0004638043232824572</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003839268978225562</v>
+        <v>0.0003839268978225555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003957260291865897</v>
+        <v>0.0003957260291872756</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003398823232683074</v>
+        <v>0.000339882323268307</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001168724359204892</v>
+        <v>0.001168724359204894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0291060033770314</v>
+        <v>0.02910600337703034</v>
       </c>
     </row>
     <row r="6">
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3470156897081064</v>
+        <v>0.3470156897081056</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1742114073783753</v>
+        <v>0.1742114073783752</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1264708581013534</v>
+        <v>0.1264708581013535</v>
       </c>
       <c r="G6" t="n">
         <v>0.01512053462978461</v>
       </c>
       <c r="H6" t="n">
-        <v>4.627778588802687e-05</v>
+        <v>4.627778588802682e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.427256342897692e-05</v>
+        <v>8.427256342897677e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002727500360475493</v>
+        <v>0.0002727500360475498</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000333125007998954</v>
+        <v>0.0003331250079989536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002619602979930308</v>
+        <v>0.0002619602979925605</v>
       </c>
       <c r="M6" t="n">
         <v>0.0003004277448122441</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008080719002817884</v>
+        <v>0.0008080719002817896</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600426214244</v>
+        <v>0.02910600426214216</v>
       </c>
     </row>
     <row r="7">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2761741634109744</v>
+        <v>0.276174163410974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1670001535399246</v>
+        <v>0.1670001535399248</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08366413169612782</v>
+        <v>0.08366413169612831</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.004937697265714205</v>
+        <v>-0.004937697265714171</v>
       </c>
       <c r="H7" t="n">
-        <v>1.121067028185039e-05</v>
+        <v>1.12106702818505e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.928231993952035e-05</v>
+        <v>3.928231993952055e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001179691972618888</v>
+        <v>0.0001179691972618887</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002831740359223623</v>
+        <v>0.0002831740359223611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001696270356181512</v>
+        <v>0.0001696270356176103</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002698716403295495</v>
+        <v>0.0002698716403295494</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004504357304151712</v>
+        <v>0.0004504357304151745</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600481086772</v>
+        <v>0.02910600481086711</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2620763088575089</v>
+        <v>0.2620763088575088</v>
       </c>
       <c r="E8" t="n">
-        <v>0.165035449895415</v>
+        <v>0.1650354498954149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0754582083088932</v>
+        <v>0.0754582083088931</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008676015011131997</v>
+        <v>-0.008676015011131983</v>
       </c>
       <c r="H8" t="n">
-        <v>3.56239416742364e-06</v>
+        <v>3.562394167423636e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.183983614280515e-05</v>
+        <v>3.183983614280502e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.560562487960585e-05</v>
+        <v>8.560562487960501e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002684537004831268</v>
+        <v>0.0002684537004831265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001495133400146371</v>
+        <v>0.0001495133400148695</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002632184485004548</v>
+        <v>0.0002632184485004554</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003504674230908818</v>
+        <v>0.0003504674230908813</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0291060048970537</v>
+        <v>0.02910600489705359</v>
       </c>
     </row>
     <row r="9">
@@ -1474,37 +1474,37 @@
         <v>0.4378111277657809</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1822659711988444</v>
+        <v>0.1822659711988445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1821547836721258</v>
+        <v>0.1821547836721257</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04134214626745768</v>
+        <v>0.04134214626745761</v>
       </c>
       <c r="H9" t="n">
-        <v>8.798208131902881e-05</v>
+        <v>8.798208131902848e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000138014185136545</v>
+        <v>0.0001380141851365453</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004426989295353248</v>
+        <v>0.0004426989295353267</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000379624658811963</v>
+        <v>0.0003796246588119625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003754309712545094</v>
+        <v>0.0003754309712549646</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003427765497631473</v>
+        <v>0.0003427765497631437</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001175695747841813</v>
+        <v>0.001175695747841808</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600350369064</v>
+        <v>0.02910600350369036</v>
       </c>
     </row>
     <row r="10">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3412637222584257</v>
+        <v>0.3412637222584256</v>
       </c>
       <c r="E10" t="n">
         <v>0.1735186361978786</v>
@@ -1531,31 +1531,31 @@
         <v>0.1230752955770191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01355015218311554</v>
+        <v>0.01355015218311549</v>
       </c>
       <c r="H10" t="n">
-        <v>4.281361698979363e-05</v>
+        <v>4.281361698979369e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>8.42909451062986e-05</v>
+        <v>8.429094510629887e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002471518015613615</v>
+        <v>0.000247151801561361</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003291111247146678</v>
+        <v>0.0003291111247146677</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002534848688862133</v>
+        <v>0.0002534848688861409</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003092144791355733</v>
+        <v>0.0003092144791355738</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007475671624110944</v>
+        <v>0.0007475671624110939</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600430160748</v>
+        <v>0.02910600430160742</v>
       </c>
     </row>
     <row r="11">
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2819651089329695</v>
+        <v>0.2819651089329694</v>
       </c>
       <c r="E11" t="n">
         <v>0.1682601739045025</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08674052130225905</v>
+        <v>0.08674052130225883</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.003602093331550962</v>
+        <v>-0.003602093331551</v>
       </c>
       <c r="H11" t="n">
-        <v>1.561661817671832e-05</v>
+        <v>1.561661817671804e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>4.624225401687235e-05</v>
+        <v>4.624225401687266e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001379871920300388</v>
+        <v>0.0001379871920300356</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002943872889499769</v>
+        <v>0.0002943872889499766</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001800216207149133</v>
+        <v>0.0001800216207148012</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002740818955873554</v>
+        <v>0.0002740818955873534</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005121653923314337</v>
+        <v>0.0005121653923313846</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600479595155</v>
+        <v>0.02910600479595188</v>
       </c>
     </row>
   </sheetData>
@@ -1765,70 +1765,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.8318367627511996</v>
+        <v>-0.8318367627511341</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.546911021552862</v>
+        <v>-1.546911021552864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3361964245403631</v>
+        <v>0.3361964245403627</v>
       </c>
       <c r="G2" t="n">
-        <v>2.965692463811946e-07</v>
+        <v>2.965692463811938e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.299317534700954e-06</v>
+        <v>8.299317534700949e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001241453184301919</v>
+        <v>0.0001241453184301911</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004125926775383893</v>
+        <v>0.000412592677538388</v>
       </c>
       <c r="K2" t="n">
-        <v>2.377451606960572e-05</v>
+        <v>2.377451606960574e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27885933319245e-05</v>
+        <v>1.278859333192298e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.531282222773776e-05</v>
+        <v>8.531282222773754e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008406755564804134</v>
+        <v>0.008406755564804127</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00432978508139235</v>
+        <v>0.004329785081392348</v>
       </c>
       <c r="P2" t="n">
-        <v>5.201863325538562e-05</v>
+        <v>5.201863325538567e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04431641876335804</v>
+        <v>0.04431641876338697</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003371153386280823</v>
+        <v>0.0003371153386280894</v>
       </c>
       <c r="S2" t="n">
-        <v>6.08577072309319e-06</v>
+        <v>6.085770723093074e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2289955955271895</v>
+        <v>0.2289955955271886</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04227130992846678</v>
+        <v>0.04227130992846669</v>
       </c>
       <c r="V2" t="n">
         <v>3.147626829962405e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004016718775058498</v>
+        <v>0.0004016718775058495</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01485851061258493</v>
+        <v>0.01485851061258492</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03423216646391793</v>
+        <v>0.03423216646391794</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1849,61 +1849,61 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.8899286417722683</v>
+        <v>-0.8899286417722736</v>
       </c>
       <c r="E3" t="n">
         <v>-1.551698971083271</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3024108743409475</v>
+        <v>0.3024108743409471</v>
       </c>
       <c r="G3" t="n">
-        <v>2.913556405602289e-07</v>
+        <v>2.913556405602291e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.192447662063789e-06</v>
+        <v>8.19244766206374e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001182094654764928</v>
+        <v>0.0001182094654764929</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003790579604269334</v>
+        <v>0.0003790579604269342</v>
       </c>
       <c r="K3" t="n">
-        <v>2.255464133251986e-05</v>
+        <v>2.255464133251988e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.560365380602751e-06</v>
+        <v>9.560365380601449e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.320443945428961e-05</v>
+        <v>7.320443945428972e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006668732196496188</v>
+        <v>0.006668732196496181</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004028407106369552</v>
+        <v>0.004028407106369559</v>
       </c>
       <c r="P3" t="n">
-        <v>4.461104723036824e-05</v>
+        <v>4.461104723036827e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04229854053954429</v>
+        <v>0.04229854053953782</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003255742193480538</v>
+        <v>0.000325574219348054</v>
       </c>
       <c r="S3" t="n">
-        <v>5.806137719731432e-06</v>
+        <v>5.806137719731486e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2175915407940364</v>
+        <v>0.2175915407940366</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04025218641642344</v>
+        <v>0.04025218641642348</v>
       </c>
       <c r="V3" t="n">
-        <v>3.068919424822657e-06</v>
+        <v>3.068919424822648e-06</v>
       </c>
       <c r="W3" t="n">
         <v>0.0003769658717695396</v>
@@ -1912,7 +1912,7 @@
         <v>0.01394968134156842</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03320322703650667</v>
+        <v>0.0332032270365067</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9325568588032782</v>
+        <v>-0.9325568588032916</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.555551321266468</v>
+        <v>-1.555551321266467</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2739584574408703</v>
+        <v>0.2739584574408708</v>
       </c>
       <c r="G4" t="n">
-        <v>2.89121440208585e-07</v>
+        <v>2.891214402085847e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.089359089440916e-06</v>
+        <v>8.089359089440964e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000113669514786057</v>
+        <v>0.0001136695147860584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003818725925983408</v>
+        <v>0.00038187259259834</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208616895876113e-05</v>
+        <v>2.208616895876115e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.142570379069835e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.406447584143276e-05</v>
+        <v>6.406447584143261e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007437704532451568</v>
+        <v>0.007437704532451571</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003624892587084511</v>
+        <v>0.003624892587084502</v>
       </c>
       <c r="P4" t="n">
         <v>3.895583381334161e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04084272446108819</v>
+        <v>0.04084272446110264</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003068520323935458</v>
+        <v>0.0003068520323935346</v>
       </c>
       <c r="S4" t="n">
-        <v>5.70332687947939e-06</v>
+        <v>5.703326879479336e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2100369267969589</v>
+        <v>0.210036926796959</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03954559184252722</v>
+        <v>0.03954559184252743</v>
       </c>
       <c r="V4" t="n">
-        <v>3.043074396944944e-06</v>
+        <v>3.043074396944945e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003781714583220808</v>
+        <v>0.0003781714583220806</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01395357111282989</v>
+        <v>0.01395357111282993</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03226032871386394</v>
+        <v>0.03226032871386401</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,70 +2017,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9610042797344152</v>
+        <v>-0.9610042797343921</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.558078749691934</v>
+        <v>-1.558078749691933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2686658744523958</v>
+        <v>0.2686658744523964</v>
       </c>
       <c r="G5" t="n">
-        <v>2.897866351763603e-07</v>
+        <v>2.897866351763606e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.952851542098839e-06</v>
+        <v>7.952851542098832e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001089211340744995</v>
+        <v>0.0001089211340744994</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000377383695230042</v>
+        <v>0.0003773836952300434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.849084162415461e-05</v>
+        <v>1.849084162415463e-05</v>
       </c>
       <c r="L5" t="n">
         <v>1.576023537294646e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.752074266559432e-05</v>
+        <v>6.752074266559439e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009473451012546366</v>
+        <v>0.009473451012544109</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003178356408303755</v>
+        <v>0.003178356408303753</v>
       </c>
       <c r="P5" t="n">
-        <v>4.098098693924275e-05</v>
+        <v>4.098098693924283e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03825761146183003</v>
+        <v>0.03825761146181197</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002854582417799102</v>
+        <v>0.0002854582417799095</v>
       </c>
       <c r="S5" t="n">
-        <v>5.692182092243645e-06</v>
+        <v>5.692182092243681e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1909427155801542</v>
+        <v>0.190942715580153</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03949088528806882</v>
+        <v>0.03949088528806881</v>
       </c>
       <c r="V5" t="n">
-        <v>2.888630117398987e-06</v>
+        <v>2.888630117398988e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003950802924558245</v>
+        <v>0.0003950802924558246</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01450133346268057</v>
+        <v>0.01450133346268053</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03123778130870591</v>
+        <v>0.03123778130870588</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2101,58 +2101,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.214345340757552</v>
+        <v>-1.214345340757594</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.581940595563526</v>
+        <v>-1.581940595563529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2172759522144014</v>
+        <v>0.2172759522144011</v>
       </c>
       <c r="G6" t="n">
-        <v>2.647205223344927e-07</v>
+        <v>2.647205223344928e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.033033267627491e-06</v>
+        <v>7.033033267627473e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.405339871544763e-05</v>
+        <v>6.405339871544764e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002323590279980933</v>
+        <v>0.000232359027998093</v>
       </c>
       <c r="K6" t="n">
-        <v>9.590224339855896e-06</v>
+        <v>9.590224339855894e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.473351551477942e-06</v>
+        <v>4.473351551477947e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.184655774664004e-05</v>
+        <v>3.184655774664003e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003582979316755783</v>
+        <v>0.003582979316743277</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001497757878139536</v>
+        <v>0.001497757878139535</v>
       </c>
       <c r="P6" t="n">
-        <v>2.009157345048727e-05</v>
+        <v>2.009157345048726e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01758459928194833</v>
+        <v>0.01758459928196839</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001284309419507245</v>
+        <v>0.0001284309419507246</v>
       </c>
       <c r="S6" t="n">
-        <v>4.008760422790602e-06</v>
+        <v>4.008760422790605e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06289437900603601</v>
+        <v>0.06289437900603606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02789301190265932</v>
+        <v>0.02789301190265926</v>
       </c>
       <c r="V6" t="n">
         <v>2.420562301944111e-06</v>
@@ -2161,10 +2161,10 @@
         <v>0.0003170905511888872</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01153573242447724</v>
+        <v>0.01153573242447717</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02450914549601222</v>
+        <v>0.02450914549601206</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.41018262152461</v>
+        <v>-1.410182621524585</v>
       </c>
       <c r="E7" t="n">
         <v>-1.601206211225018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1547429780330187</v>
+        <v>0.1547429780330178</v>
       </c>
       <c r="G7" t="n">
-        <v>2.446044256251518e-07</v>
+        <v>2.446044256251515e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442096151646438e-06</v>
+        <v>6.442096151646407e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770422375687465e-05</v>
+        <v>2.770422375687518e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001298426255663869</v>
+        <v>0.0001298426255663872</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.396929241751816e-06</v>
+        <v>-8.396929241751826e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>5.805497197925381e-07</v>
+        <v>5.805497197919515e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.000391007392922e-05</v>
+        <v>-2.000391007392921e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00126832053984055</v>
+        <v>0.001268320539847134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002331686864616764</v>
+        <v>0.0002331686864616773</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.077758791439363e-05</v>
+        <v>-1.077758791439362e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003018109874449845</v>
+        <v>0.003018109874445207</v>
       </c>
       <c r="R7" t="n">
-        <v>5.341088397340722e-05</v>
+        <v>5.34108839734073e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.815905774000151e-06</v>
+        <v>2.815905774000133e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01811159063342163</v>
+        <v>-0.01811159063342173</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02014517267249237</v>
+        <v>0.0201451726724924</v>
       </c>
       <c r="V7" t="n">
-        <v>1.625285506723567e-06</v>
+        <v>1.625285506723564e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002774825994218636</v>
+        <v>0.0002774825994218644</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009834654166229096</v>
+        <v>0.009834654166229129</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01943177570532379</v>
+        <v>0.01943177570532376</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.453464828470351</v>
+        <v>-1.453464828470376</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.606201264717672</v>
+        <v>-1.606201264717674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1400943034061186</v>
+        <v>0.1400943034061174</v>
       </c>
       <c r="G8" t="n">
-        <v>2.393217858839121e-07</v>
+        <v>2.393217858839118e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3355442135307e-06</v>
+        <v>6.335544213530667e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.010386983685864e-05</v>
+        <v>2.010386983685856e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.458790381058682e-05</v>
+        <v>5.458790381037149e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.273154749541741e-05</v>
+        <v>-1.273154749541744e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.189015532855261e-07</v>
+        <v>-6.189015532872036e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.06674876149983e-05</v>
+        <v>-2.066748761499836e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005453538392433332</v>
+        <v>0.0005453538392290258</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001999270889226519</v>
+        <v>0.0001999270889226515</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.130433784507032e-05</v>
+        <v>-1.130433784507029e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0001009093017733491</v>
+        <v>-0.0001009093017669441</v>
       </c>
       <c r="R8" t="n">
-        <v>5.046903136687023e-05</v>
+        <v>5.046903136687012e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.523538981750807e-06</v>
+        <v>2.523538981750777e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.03419117807884189</v>
+        <v>-0.03419117807884192</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01832117629705292</v>
+        <v>0.01832117629705289</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47286592199158e-06</v>
+        <v>1.472865921991581e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002642465629666145</v>
+        <v>0.0002642465629666147</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009325281105489483</v>
+        <v>0.009325281105489471</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01818779607301859</v>
+        <v>0.0181877960730185</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2353,70 +2353,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9816773943303297</v>
+        <v>-0.9816773943303504</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.560477678769052</v>
+        <v>-1.560477678769051</v>
       </c>
       <c r="F9" t="n">
-        <v>0.275970089963966</v>
+        <v>0.2759700899639653</v>
       </c>
       <c r="G9" t="n">
-        <v>2.837014222025344e-07</v>
+        <v>2.837014222025333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.000478904578948e-06</v>
+        <v>8.000478904578813e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000103964683031186</v>
+        <v>0.0001039646830311864</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003206668189657264</v>
+        <v>0.0003206668189657246</v>
       </c>
       <c r="K9" t="n">
-        <v>1.725475435027219e-05</v>
+        <v>1.725475435027212e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.32738216073832e-06</v>
+        <v>8.327382160729841e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>5.250591226733487e-05</v>
+        <v>5.250591226733452e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005819705930076546</v>
+        <v>0.005819705930074793</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003747769325567633</v>
+        <v>0.00374776932556763</v>
       </c>
       <c r="P9" t="n">
-        <v>3.21352896783406e-05</v>
+        <v>3.213528967834039e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03583693923637341</v>
+        <v>0.03583693923638698</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002875038294114484</v>
+        <v>0.0002875038294114476</v>
       </c>
       <c r="S9" t="n">
-        <v>5.343192153412978e-06</v>
+        <v>5.343192153412972e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1752259021330018</v>
+        <v>0.1752259021330012</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03703092045341571</v>
+        <v>0.03703092045341563</v>
       </c>
       <c r="V9" t="n">
-        <v>2.812444396054673e-06</v>
+        <v>2.812444396054669e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003599048957664525</v>
+        <v>0.0003599048957664521</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0132630592325125</v>
+        <v>0.01326305923251249</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03070715431737232</v>
+        <v>0.03070715431737227</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.242785891600649</v>
+        <v>-1.242785891600673</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.583954092606446</v>
+        <v>-1.583954092606448</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2009807515308777</v>
+        <v>0.2009807515308773</v>
       </c>
       <c r="G10" t="n">
-        <v>2.606535231856384e-07</v>
+        <v>2.606535231856346e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.341437177856521e-06</v>
+        <v>7.341437177856551e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>5.804183610040404e-05</v>
+        <v>5.804183610040383e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001991641288363848</v>
+        <v>0.0001991641288363846</v>
       </c>
       <c r="K10" t="n">
-        <v>5.74827032645292e-06</v>
+        <v>5.74827032645293e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>4.373156858208406e-06</v>
+        <v>4.373156858208395e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.019497989518515e-05</v>
+        <v>-1.01949798951852e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003432318404492637</v>
+        <v>0.003432318404490959</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005593551573233542</v>
+        <v>0.0005593551573233541</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.042040348344e-06</v>
+        <v>-5.042040348344032e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01626330145092553</v>
+        <v>0.01626330145089593</v>
       </c>
       <c r="R10" t="n">
         <v>0.0001911896163490691</v>
       </c>
       <c r="S10" t="n">
-        <v>3.880986824142107e-06</v>
+        <v>3.880986824142086e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0565555934546325</v>
+        <v>0.05655559345463235</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02720475041928916</v>
+        <v>0.02720475041928912</v>
       </c>
       <c r="V10" t="n">
-        <v>2.265845353073728e-06</v>
+        <v>2.265845353073727e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003161481518067735</v>
+        <v>0.0003161481518067732</v>
       </c>
       <c r="X10" t="n">
         <v>0.0113753928393393</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02402352640323898</v>
+        <v>0.02402352640323894</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2521,70 +2521,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.385688274388546</v>
+        <v>-1.385688274388556</v>
       </c>
       <c r="E11" t="n">
         <v>-1.597390680708501</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1665538562409583</v>
+        <v>0.1665538562409579</v>
       </c>
       <c r="G11" t="n">
-        <v>2.486819275140102e-07</v>
+        <v>2.486819275140079e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.49012451281605e-06</v>
+        <v>6.490124512816031e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240530691326567e-05</v>
+        <v>3.240530691326464e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001303519905026394</v>
+        <v>0.0001303519905024281</v>
       </c>
       <c r="K11" t="n">
-        <v>4.233469589935449e-06</v>
+        <v>4.233469589935256e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.852182648276856e-06</v>
+        <v>1.852182648274243e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.635750525645162e-05</v>
+        <v>-1.63575052564516e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001951223356240781</v>
+        <v>0.001951223356248478</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002094303248603937</v>
+        <v>0.0002094303248604139</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.524319044482312e-06</v>
+        <v>-8.524319044482572e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004286897569943299</v>
+        <v>0.004286897569940568</v>
       </c>
       <c r="R11" t="n">
-        <v>6.320468555707538e-05</v>
+        <v>6.320468555721794e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.004742308581588e-06</v>
+        <v>3.004742308581565e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01366391878408753</v>
+        <v>-0.01366391878408773</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02136100704048478</v>
+        <v>0.02136100704048463</v>
       </c>
       <c r="V11" t="n">
-        <v>2.170451989898062e-06</v>
+        <v>2.170451989898054e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002897501746590912</v>
+        <v>0.000289750174659091</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01030009914522403</v>
+        <v>0.01030009914522407</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02019495089303869</v>
+        <v>0.02019495089303859</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.6052801200194742</v>
+        <v>-0.605280120019521</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.546911021552862</v>
+        <v>-1.546911021552864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5627530673585396</v>
+        <v>0.5627530673585389</v>
       </c>
       <c r="G2" t="n">
-        <v>2.965692463811946e-07</v>
+        <v>2.965692463811938e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.299317534700954e-06</v>
+        <v>8.299317534700949e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001241453184301919</v>
+        <v>0.0001241453184301911</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004125926775383893</v>
+        <v>0.000412592677538388</v>
       </c>
       <c r="K2" t="n">
-        <v>2.377451606960572e-05</v>
+        <v>2.377451606960574e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27885933319245e-05</v>
+        <v>1.278859333192298e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.531282222773776e-05</v>
+        <v>8.531282222773754e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008406755564804134</v>
+        <v>0.008406755564804127</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00432978508139235</v>
+        <v>0.004329785081392348</v>
       </c>
       <c r="P2" t="n">
-        <v>5.201863325538562e-05</v>
+        <v>5.201863325538567e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04431641876335804</v>
+        <v>0.04431641876338697</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003371153386280823</v>
+        <v>0.0003371153386280894</v>
       </c>
       <c r="S2" t="n">
-        <v>6.08577072309319e-06</v>
+        <v>6.085770723093074e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2289955955271895</v>
+        <v>0.2289955955271886</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04227130992846678</v>
+        <v>0.04227130992846669</v>
       </c>
       <c r="V2" t="n">
         <v>3.147626829962405e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004016718775058498</v>
+        <v>0.0004016718775058495</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01485851061258493</v>
+        <v>0.01485851061258492</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03423216646391793</v>
+        <v>0.03423216646391794</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2830,61 +2830,61 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.7225435171623454</v>
+        <v>-0.7225435171623522</v>
       </c>
       <c r="E3" t="n">
         <v>-1.551698971083271</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4697959990148228</v>
+        <v>0.4697959990148232</v>
       </c>
       <c r="G3" t="n">
-        <v>2.913556405602289e-07</v>
+        <v>2.913556405602291e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.192447662063789e-06</v>
+        <v>8.19244766206374e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001182094654764928</v>
+        <v>0.0001182094654764929</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003790579604269334</v>
+        <v>0.0003790579604269342</v>
       </c>
       <c r="K3" t="n">
-        <v>2.255464133251986e-05</v>
+        <v>2.255464133251988e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.560365380602751e-06</v>
+        <v>9.560365380601449e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.320443945428961e-05</v>
+        <v>7.320443945428972e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006668732196496188</v>
+        <v>0.006668732196496181</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004028407106369552</v>
+        <v>0.004028407106369559</v>
       </c>
       <c r="P3" t="n">
-        <v>4.461104723036824e-05</v>
+        <v>4.461104723036827e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04229854053954429</v>
+        <v>0.04229854053953782</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003255742193480538</v>
+        <v>0.000325574219348054</v>
       </c>
       <c r="S3" t="n">
-        <v>5.806137719731432e-06</v>
+        <v>5.806137719731486e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2175915407940364</v>
+        <v>0.2175915407940366</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04025218641642344</v>
+        <v>0.04025218641642348</v>
       </c>
       <c r="V3" t="n">
-        <v>3.068919424822657e-06</v>
+        <v>3.068919424822648e-06</v>
       </c>
       <c r="W3" t="n">
         <v>0.0003769658717695396</v>
@@ -2893,7 +2893,7 @@
         <v>0.01394968134156842</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03320322703650667</v>
+        <v>0.0332032270365067</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7960333563638793</v>
+        <v>-0.7960333563638701</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.555551321266468</v>
+        <v>-1.555551321266467</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4104819599324461</v>
+        <v>0.4104819599324452</v>
       </c>
       <c r="G4" t="n">
-        <v>2.89121440208585e-07</v>
+        <v>2.891214402085847e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.089359089440916e-06</v>
+        <v>8.089359089440964e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000113669514786057</v>
+        <v>0.0001136695147860584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003818725925983408</v>
+        <v>0.00038187259259834</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208616895876113e-05</v>
+        <v>2.208616895876115e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.142570379069835e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.406447584143276e-05</v>
+        <v>6.406447584143261e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007437704532451568</v>
+        <v>0.007437704532451571</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003624892587084511</v>
+        <v>0.003624892587084502</v>
       </c>
       <c r="P4" t="n">
         <v>3.895583381334161e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04084272446108819</v>
+        <v>0.04084272446110264</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003068520323935458</v>
+        <v>0.0003068520323935346</v>
       </c>
       <c r="S4" t="n">
-        <v>5.70332687947939e-06</v>
+        <v>5.703326879479336e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2100369267969589</v>
+        <v>0.210036926796959</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03954559184252722</v>
+        <v>0.03954559184252743</v>
       </c>
       <c r="V4" t="n">
-        <v>3.043074396944944e-06</v>
+        <v>3.043074396944945e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003781714583220808</v>
+        <v>0.0003781714583220806</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01395357111282989</v>
+        <v>0.01395357111282993</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03226032871386394</v>
+        <v>0.03226032871386401</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,70 +2998,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8401332055963163</v>
+        <v>-0.8401332055963089</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.558078749691934</v>
+        <v>-1.558078749691933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3895369486366633</v>
+        <v>0.3895369486366646</v>
       </c>
       <c r="G5" t="n">
-        <v>2.897866351763603e-07</v>
+        <v>2.897866351763606e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.952851542098839e-06</v>
+        <v>7.952851542098832e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001089211340744995</v>
+        <v>0.0001089211340744994</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000377383695230042</v>
+        <v>0.0003773836952300434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.849084162415461e-05</v>
+        <v>1.849084162415463e-05</v>
       </c>
       <c r="L5" t="n">
         <v>1.576023537294646e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.752074266559432e-05</v>
+        <v>6.752074266559439e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009473451012546366</v>
+        <v>0.009473451012544109</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003178356408303755</v>
+        <v>0.003178356408303753</v>
       </c>
       <c r="P5" t="n">
-        <v>4.098098693924275e-05</v>
+        <v>4.098098693924283e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03825761146183003</v>
+        <v>0.03825761146181197</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002854582417799102</v>
+        <v>0.0002854582417799095</v>
       </c>
       <c r="S5" t="n">
-        <v>5.692182092243645e-06</v>
+        <v>5.692182092243681e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1909427155801542</v>
+        <v>0.190942715580153</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03949088528806882</v>
+        <v>0.03949088528806881</v>
       </c>
       <c r="V5" t="n">
-        <v>2.888630117398987e-06</v>
+        <v>2.888630117398988e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003950802924558245</v>
+        <v>0.0003950802924558246</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01450133346268057</v>
+        <v>0.01450133346268053</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03123778130870591</v>
+        <v>0.03123778130870588</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3082,58 +3082,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.105000608734674</v>
+        <v>-1.105000608734675</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.581940595563526</v>
+        <v>-1.581940595563529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3266206842790851</v>
+        <v>0.3266206842790855</v>
       </c>
       <c r="G6" t="n">
-        <v>2.647205223344927e-07</v>
+        <v>2.647205223344928e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.033033267627491e-06</v>
+        <v>7.033033267627473e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.405339871544763e-05</v>
+        <v>6.405339871544764e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002323590279980933</v>
+        <v>0.000232359027998093</v>
       </c>
       <c r="K6" t="n">
-        <v>9.590224339855896e-06</v>
+        <v>9.590224339855894e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.473351551477942e-06</v>
+        <v>4.473351551477947e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.184655774664004e-05</v>
+        <v>3.184655774664003e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003582979316755783</v>
+        <v>0.003582979316743277</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001497757878139536</v>
+        <v>0.001497757878139535</v>
       </c>
       <c r="P6" t="n">
-        <v>2.009157345048727e-05</v>
+        <v>2.009157345048726e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01758459928194833</v>
+        <v>0.01758459928196839</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001284309419507245</v>
+        <v>0.0001284309419507246</v>
       </c>
       <c r="S6" t="n">
-        <v>4.008760422790602e-06</v>
+        <v>4.008760422790605e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06289437900603601</v>
+        <v>0.06289437900603606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02789301190265932</v>
+        <v>0.02789301190265926</v>
       </c>
       <c r="V6" t="n">
         <v>2.420562301944111e-06</v>
@@ -3142,10 +3142,10 @@
         <v>0.0003170905511888872</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01153573242447724</v>
+        <v>0.01153573242447717</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02450914549601222</v>
+        <v>0.02450914549601206</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.347664511507229</v>
+        <v>-1.347664511507221</v>
       </c>
       <c r="E7" t="n">
         <v>-1.601206211225018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2172610880742657</v>
+        <v>0.2172610880742639</v>
       </c>
       <c r="G7" t="n">
-        <v>2.446044256251518e-07</v>
+        <v>2.446044256251515e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442096151646438e-06</v>
+        <v>6.442096151646407e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770422375687465e-05</v>
+        <v>2.770422375687518e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001298426255663869</v>
+        <v>0.0001298426255663872</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.396929241751816e-06</v>
+        <v>-8.396929241751826e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>5.805497197925381e-07</v>
+        <v>5.805497197919515e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.000391007392922e-05</v>
+        <v>-2.000391007392921e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00126832053984055</v>
+        <v>0.001268320539847134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002331686864616764</v>
+        <v>0.0002331686864616773</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.077758791439363e-05</v>
+        <v>-1.077758791439362e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003018109874449845</v>
+        <v>0.003018109874445207</v>
       </c>
       <c r="R7" t="n">
-        <v>5.341088397340722e-05</v>
+        <v>5.34108839734073e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.815905774000151e-06</v>
+        <v>2.815905774000133e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01811159063342163</v>
+        <v>-0.01811159063342173</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02014517267249237</v>
+        <v>0.0201451726724924</v>
       </c>
       <c r="V7" t="n">
-        <v>1.625285506723567e-06</v>
+        <v>1.625285506723564e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002774825994218636</v>
+        <v>0.0002774825994218644</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009834654166229096</v>
+        <v>0.009834654166229129</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01943177570532379</v>
+        <v>0.01943177570532376</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.399302573322045</v>
+        <v>-1.399302573322059</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.606201264717672</v>
+        <v>-1.606201264717674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1942565585751332</v>
+        <v>0.1942565585751311</v>
       </c>
       <c r="G8" t="n">
-        <v>2.393217858839121e-07</v>
+        <v>2.393217858839118e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3355442135307e-06</v>
+        <v>6.335544213530667e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.010386983685864e-05</v>
+        <v>2.010386983685856e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.458790381058682e-05</v>
+        <v>5.458790381037149e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.273154749541741e-05</v>
+        <v>-1.273154749541744e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.189015532855261e-07</v>
+        <v>-6.189015532872036e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.06674876149983e-05</v>
+        <v>-2.066748761499836e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005453538392433332</v>
+        <v>0.0005453538392290258</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001999270889226519</v>
+        <v>0.0001999270889226515</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.130433784507032e-05</v>
+        <v>-1.130433784507029e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0001009093017733491</v>
+        <v>-0.0001009093017669441</v>
       </c>
       <c r="R8" t="n">
-        <v>5.046903136687023e-05</v>
+        <v>5.046903136687012e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.523538981750807e-06</v>
+        <v>2.523538981750777e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.03419117807884189</v>
+        <v>-0.03419117807884192</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01832117629705292</v>
+        <v>0.01832117629705289</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47286592199158e-06</v>
+        <v>1.472865921991581e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002642465629666145</v>
+        <v>0.0002642465629666147</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009325281105489483</v>
+        <v>0.009325281105489471</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01818779607301859</v>
+        <v>0.0181877960730185</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3334,70 +3334,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8250054441437022</v>
+        <v>-0.8250054441436981</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.560477678769052</v>
+        <v>-1.560477678769051</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4326420402104575</v>
+        <v>0.4326420402104562</v>
       </c>
       <c r="G9" t="n">
-        <v>2.837014222025344e-07</v>
+        <v>2.837014222025333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.000478904578948e-06</v>
+        <v>8.000478904578813e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000103964683031186</v>
+        <v>0.0001039646830311864</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003206668189657264</v>
+        <v>0.0003206668189657246</v>
       </c>
       <c r="K9" t="n">
-        <v>1.725475435027219e-05</v>
+        <v>1.725475435027212e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.32738216073832e-06</v>
+        <v>8.327382160729841e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>5.250591226733487e-05</v>
+        <v>5.250591226733452e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005819705930076546</v>
+        <v>0.005819705930074793</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003747769325567633</v>
+        <v>0.00374776932556763</v>
       </c>
       <c r="P9" t="n">
-        <v>3.21352896783406e-05</v>
+        <v>3.213528967834039e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03583693923637341</v>
+        <v>0.03583693923638698</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002875038294114484</v>
+        <v>0.0002875038294114476</v>
       </c>
       <c r="S9" t="n">
-        <v>5.343192153412978e-06</v>
+        <v>5.343192153412972e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1752259021330018</v>
+        <v>0.1752259021330012</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03703092045341571</v>
+        <v>0.03703092045341563</v>
       </c>
       <c r="V9" t="n">
-        <v>2.812444396054673e-06</v>
+        <v>2.812444396054669e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003599048957664525</v>
+        <v>0.0003599048957664521</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0132630592325125</v>
+        <v>0.01326305923251249</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03070715431737232</v>
+        <v>0.03070715431737227</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.155371334932199</v>
+        <v>-1.155371334932196</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.583954092606446</v>
+        <v>-1.583954092606448</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2883953082327527</v>
+        <v>0.2883953082327533</v>
       </c>
       <c r="G10" t="n">
-        <v>2.606535231856384e-07</v>
+        <v>2.606535231856346e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.341437177856521e-06</v>
+        <v>7.341437177856551e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>5.804183610040404e-05</v>
+        <v>5.804183610040383e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001991641288363848</v>
+        <v>0.0001991641288363846</v>
       </c>
       <c r="K10" t="n">
-        <v>5.74827032645292e-06</v>
+        <v>5.74827032645293e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>4.373156858208406e-06</v>
+        <v>4.373156858208395e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.019497989518515e-05</v>
+        <v>-1.01949798951852e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003432318404492637</v>
+        <v>0.003432318404490959</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005593551573233542</v>
+        <v>0.0005593551573233541</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.042040348344e-06</v>
+        <v>-5.042040348344032e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01626330145092553</v>
+        <v>0.01626330145089593</v>
       </c>
       <c r="R10" t="n">
         <v>0.0001911896163490691</v>
       </c>
       <c r="S10" t="n">
-        <v>3.880986824142107e-06</v>
+        <v>3.880986824142086e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0565555934546325</v>
+        <v>0.05655559345463235</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02720475041928916</v>
+        <v>0.02720475041928912</v>
       </c>
       <c r="V10" t="n">
-        <v>2.265845353073728e-06</v>
+        <v>2.265845353073727e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003161481518067735</v>
+        <v>0.0003161481518067732</v>
       </c>
       <c r="X10" t="n">
         <v>0.0113753928393393</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02402352640323898</v>
+        <v>0.02402352640323894</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.329995648248197</v>
+        <v>-1.329995648248209</v>
       </c>
       <c r="E11" t="n">
         <v>-1.597390680708501</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2222464824025759</v>
+        <v>0.2222464824025765</v>
       </c>
       <c r="G11" t="n">
-        <v>2.486819275140102e-07</v>
+        <v>2.486819275140079e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.49012451281605e-06</v>
+        <v>6.490124512816031e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240530691326567e-05</v>
+        <v>3.240530691326464e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001303519905026394</v>
+        <v>0.0001303519905024281</v>
       </c>
       <c r="K11" t="n">
-        <v>4.233469589935449e-06</v>
+        <v>4.233469589935256e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.852182648276856e-06</v>
+        <v>1.852182648274243e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.635750525645162e-05</v>
+        <v>-1.63575052564516e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001951223356240781</v>
+        <v>0.001951223356248478</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002094303248603937</v>
+        <v>0.0002094303248604139</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.524319044482312e-06</v>
+        <v>-8.524319044482572e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004286897569943299</v>
+        <v>0.004286897569940568</v>
       </c>
       <c r="R11" t="n">
-        <v>6.320468555707538e-05</v>
+        <v>6.320468555721794e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.004742308581588e-06</v>
+        <v>3.004742308581565e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01366391878408753</v>
+        <v>-0.01366391878408773</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02136100704048478</v>
+        <v>0.02136100704048463</v>
       </c>
       <c r="V11" t="n">
-        <v>2.170451989898062e-06</v>
+        <v>2.170451989898054e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002897501746590912</v>
+        <v>0.000289750174659091</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01030009914522403</v>
+        <v>0.01030009914522407</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02019495089303869</v>
+        <v>0.02019495089303859</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>

--- a/Results/Methanol/methanol climate change image breakdown results.xlsx
+++ b/Results/Methanol/methanol climate change image breakdown results.xlsx
@@ -518,37 +518,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7637053688642201</v>
+        <v>0.7637053688642205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1867935009068543</v>
+        <v>0.1867935009068545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4923714659308646</v>
+        <v>0.4923714659308647</v>
       </c>
       <c r="G2" t="n">
         <v>0.05200835814725645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001067732353612939</v>
+        <v>0.000106773235361294</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001628208042780026</v>
+        <v>0.0001628208042780028</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005286314349593282</v>
+        <v>0.0005286314349593293</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004139107301173978</v>
+        <v>0.0004139107301173979</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004318159917828688</v>
+        <v>0.0004318159917828682</v>
       </c>
       <c r="M2" t="n">
         <v>0.0003589945926490613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001423100974447686</v>
+        <v>0.001423100974447685</v>
       </c>
       <c r="O2" t="n">
         <v>0.02910599611564924</v>
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7587127580564583</v>
+        <v>0.7587127580564584</v>
       </c>
       <c r="E3" t="n">
         <v>0.1853863416547732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4910773732529227</v>
+        <v>0.4910773732529228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04986741037531069</v>
+        <v>0.04986741037531093</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001020728379294524</v>
+        <v>0.0001020728379294522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001543848552269669</v>
+        <v>0.000154384855226967</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005033555848161309</v>
+        <v>0.0005033555848161314</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004035815179113719</v>
+        <v>0.0004035815179113726</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004154471741203773</v>
+        <v>0.0004154471741202172</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003528653539079979</v>
+        <v>0.0003528653539079976</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001343929378793109</v>
+        <v>0.001343929378793097</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599607074627</v>
+        <v>0.02910599607074615</v>
       </c>
     </row>
     <row r="4">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7555157706438176</v>
+        <v>0.755515770643818</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1843045463719576</v>
+        <v>0.1843045463719578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.490206509128582</v>
+        <v>0.4902065091285821</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04878455486382769</v>
+        <v>0.04878455486382766</v>
       </c>
       <c r="H4" t="n">
-        <v>9.927352951629176e-05</v>
+        <v>9.927352951629143e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001491813170349978</v>
+        <v>0.0001491813170349936</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004840237189151329</v>
+        <v>0.0004840237189151331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003907306092057171</v>
+        <v>0.0003907306092057179</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004068474043467823</v>
+        <v>0.0004068474043466362</v>
       </c>
       <c r="M4" t="n">
-        <v>0.000346111908938109</v>
+        <v>0.0003461119089381092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001237995751058908</v>
+        <v>0.00123799575105891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910599604043451</v>
+        <v>0.02910599604043473</v>
       </c>
     </row>
     <row r="5">
@@ -677,34 +677,34 @@
         <v>0.183230353481184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4890894138049242</v>
+        <v>0.4890894138049241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04546793851780911</v>
+        <v>0.04546793851780917</v>
       </c>
       <c r="H5" t="n">
-        <v>9.433295702090335e-05</v>
+        <v>9.433295702090358e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001425295224211093</v>
+        <v>0.0001425295224211096</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004638043232824572</v>
+        <v>0.0004638043232824583</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003839268978225555</v>
+        <v>0.000383926897822556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003957260291872756</v>
+        <v>0.0003957260291869406</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000339882323268307</v>
+        <v>0.0003398823232683072</v>
       </c>
       <c r="N5" t="n">
         <v>0.001168724359204894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599598764674</v>
+        <v>0.02910599598764707</v>
       </c>
     </row>
     <row r="6">
@@ -722,37 +722,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7023771077035205</v>
+        <v>0.7023771077035206</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1742114073783752</v>
+        <v>0.1742114073783751</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4818322848993405</v>
+        <v>0.4818322848993407</v>
       </c>
       <c r="G6" t="n">
         <v>0.01512053462978461</v>
       </c>
       <c r="H6" t="n">
-        <v>4.627778588802682e-05</v>
+        <v>4.627778588802689e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.427256342897677e-05</v>
+        <v>8.427256342897686e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002727500360475498</v>
+        <v>0.0002727500360475501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003331250079989536</v>
+        <v>0.0003331250079989535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002619602979925605</v>
+        <v>0.000261960297992561</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003004277448122441</v>
+        <v>0.0003004277448122439</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008080719002817896</v>
+        <v>0.0008080719002817894</v>
       </c>
       <c r="O6" t="n">
         <v>0.02910599545957004</v>
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6685836775782195</v>
+        <v>0.6685836775782186</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1670001535399248</v>
+        <v>0.1670001535399246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4760736555836552</v>
+        <v>0.4760736555836548</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.004937697265714171</v>
+        <v>-0.004937697265714169</v>
       </c>
       <c r="H7" t="n">
-        <v>1.12106702818505e-05</v>
+        <v>1.121067028185039e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.928231993952055e-05</v>
+        <v>3.928231993952043e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001179691972618887</v>
+        <v>0.0001179691972618876</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002831740359223611</v>
+        <v>0.0002831740359223619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001696270356176103</v>
+        <v>0.0001696270356171056</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002698716403295494</v>
+        <v>0.0002698716403295492</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004504357304151745</v>
+        <v>0.0004504357304151717</v>
       </c>
       <c r="O7" t="n">
         <v>0.02910599509058576</v>
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6610223730866218</v>
+        <v>0.661022373086623</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1650354498954149</v>
+        <v>0.165035449895415</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4744042824202051</v>
+        <v>0.4744042824202049</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008676015011131983</v>
+        <v>-0.008676015011132016</v>
       </c>
       <c r="H8" t="n">
-        <v>3.562394167423636e-06</v>
+        <v>3.562394167423464e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.183983614280502e-05</v>
+        <v>3.183983614280513e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.560562487960501e-05</v>
+        <v>8.560562487960755e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002684537004831265</v>
+        <v>0.0002684537004831272</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001495133400148695</v>
+        <v>0.0001495133400159496</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002632184485004554</v>
+        <v>0.0002632184485004551</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003504674230908813</v>
+        <v>0.0003504674230908825</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599501485467</v>
+        <v>0.029105995014855</v>
       </c>
     </row>
     <row r="9">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7440488351015296</v>
+        <v>0.7440488351015292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1822659711988445</v>
+        <v>0.1822659711988444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4883924985936147</v>
+        <v>0.4883924985936146</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04134214626745761</v>
+        <v>0.04134214626745768</v>
       </c>
       <c r="H9" t="n">
-        <v>8.798208131902848e-05</v>
+        <v>8.798208131902863e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001380141851365453</v>
+        <v>0.0001380141851365448</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004426989295353267</v>
+        <v>0.0004426989295353237</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003796246588119625</v>
+        <v>0.0003796246588119624</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003754309712549646</v>
+        <v>0.0003754309712545085</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003427765497631437</v>
+        <v>0.0003427765497631469</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001175695747841808</v>
+        <v>0.00117569574784181</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599591795004</v>
+        <v>0.02910599591795038</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6994606648437897</v>
+        <v>0.6994606648437904</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1735186361978786</v>
+        <v>0.1735186361978787</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4812722470351943</v>
+        <v>0.4812722470351946</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01355015218311549</v>
+        <v>0.01355015218311555</v>
       </c>
       <c r="H10" t="n">
-        <v>4.281361698979369e-05</v>
+        <v>4.281361698979371e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>8.429094510629887e-05</v>
+        <v>8.429094510629877e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000247151801561361</v>
+        <v>0.0002471518015613611</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003291111247146677</v>
+        <v>0.0003291111247146676</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002534848688861409</v>
+        <v>0.0002534848688860881</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003092144791355738</v>
+        <v>0.0003092144791355731</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007475671624110939</v>
+        <v>0.0007475671624110949</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599542879633</v>
+        <v>0.02910599542879666</v>
       </c>
     </row>
     <row r="11">
@@ -977,40 +977,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6726614526308744</v>
+        <v>0.6726614526308753</v>
       </c>
       <c r="E11" t="n">
         <v>0.1682601739045025</v>
       </c>
       <c r="F11" t="n">
-        <v>0.47743687467801</v>
+        <v>0.4774368746780104</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.003602093331551</v>
+        <v>-0.00360209333155099</v>
       </c>
       <c r="H11" t="n">
-        <v>1.561661817671804e-05</v>
+        <v>1.56166181767182e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>4.624225401687266e-05</v>
+        <v>4.624225401687228e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001379871920300356</v>
+        <v>0.0001379871920300392</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002943872889499766</v>
+        <v>0.0002943872889499774</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001800216207148012</v>
+        <v>0.0001800216207148445</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002740818955873534</v>
+        <v>0.0002740818955873555</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005121653923313846</v>
+        <v>0.000512165392331434</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910599511810585</v>
+        <v>0.02910599511810619</v>
       </c>
     </row>
   </sheetData>
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4767783229955003</v>
+        <v>0.4767783229955005</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1867935009068543</v>
+        <v>0.1867935009068545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2054444129547423</v>
+        <v>0.2054444129547421</v>
       </c>
       <c r="G2" t="n">
         <v>0.05200835814725645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001067732353612939</v>
+        <v>0.000106773235361294</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001628208042780026</v>
+        <v>0.0001628208042780028</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005286314349593282</v>
+        <v>0.0005286314349593293</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004139107301173978</v>
+        <v>0.0004139107301173979</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004318159917828688</v>
+        <v>0.0004318159917828682</v>
       </c>
       <c r="M2" t="n">
         <v>0.0003589945926490613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001423100974447686</v>
+        <v>0.001423100974447685</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600322305168</v>
+        <v>0.02910600322305179</v>
       </c>
     </row>
     <row r="3">
@@ -1171,34 +1171,34 @@
         <v>0.1853863416547732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2005836664957467</v>
+        <v>0.2005836664957466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04986741037531069</v>
+        <v>0.04986741037531093</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001020728379294524</v>
+        <v>0.0001020728379294522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001543848552269669</v>
+        <v>0.000154384855226967</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005033555848161309</v>
+        <v>0.0005033555848161314</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004035815179113719</v>
+        <v>0.0004035815179113726</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004154471741203773</v>
+        <v>0.0004154471741202172</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003528653539079979</v>
+        <v>0.0003528653539079976</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001343929378793109</v>
+        <v>0.001343929378793097</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600326649665</v>
+        <v>0.0291060032664967</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4632709816289223</v>
+        <v>0.4632709816289229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1843045463719576</v>
+        <v>0.1843045463719578</v>
       </c>
       <c r="F4" t="n">
         <v>0.1979617128745608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04878455486382769</v>
+        <v>0.04878455486382766</v>
       </c>
       <c r="H4" t="n">
-        <v>9.927352951629176e-05</v>
+        <v>9.927352951629143e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001491813170349978</v>
+        <v>0.0001491813170349936</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004840237189151329</v>
+        <v>0.0004840237189151331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003907306092057171</v>
+        <v>0.0003907306092057179</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004068474043467823</v>
+        <v>0.0004068474043466362</v>
       </c>
       <c r="M4" t="n">
-        <v>0.000346111908938109</v>
+        <v>0.0003461119089381092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001237995751058908</v>
+        <v>0.00123799575105891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600327956026</v>
+        <v>0.02910600327956087</v>
       </c>
     </row>
     <row r="5">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4515718821068008</v>
+        <v>0.4515718821068019</v>
       </c>
       <c r="E5" t="n">
         <v>0.183230353481184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1907786603185699</v>
+        <v>0.1907786603185696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04546793851780911</v>
+        <v>0.04546793851780917</v>
       </c>
       <c r="H5" t="n">
-        <v>9.433295702090335e-05</v>
+        <v>9.433295702090358e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001425295224211093</v>
+        <v>0.0001425295224211096</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004638043232824572</v>
+        <v>0.0004638043232824583</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003839268978225555</v>
+        <v>0.000383926897822556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003957260291872756</v>
+        <v>0.0003957260291869406</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000339882323268307</v>
+        <v>0.0003398823232683072</v>
       </c>
       <c r="N5" t="n">
         <v>0.001168724359204894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600337703034</v>
+        <v>0.02910600337703201</v>
       </c>
     </row>
     <row r="6">
@@ -1318,37 +1318,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3470156897081056</v>
+        <v>0.3470156897081055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1742114073783752</v>
+        <v>0.1742114073783751</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1264708581013535</v>
+        <v>0.1264708581013534</v>
       </c>
       <c r="G6" t="n">
         <v>0.01512053462978461</v>
       </c>
       <c r="H6" t="n">
-        <v>4.627778588802682e-05</v>
+        <v>4.627778588802689e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.427256342897677e-05</v>
+        <v>8.427256342897686e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002727500360475498</v>
+        <v>0.0002727500360475501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003331250079989536</v>
+        <v>0.0003331250079989535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002619602979925605</v>
+        <v>0.000261960297992561</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003004277448122441</v>
+        <v>0.0003004277448122439</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008080719002817896</v>
+        <v>0.0008080719002817894</v>
       </c>
       <c r="O6" t="n">
         <v>0.02910600426214216</v>
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.276174163410974</v>
+        <v>0.2761741634109743</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1670001535399248</v>
+        <v>0.1670001535399246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08366413169612831</v>
+        <v>0.08366413169612791</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.004937697265714171</v>
+        <v>-0.004937697265714169</v>
       </c>
       <c r="H7" t="n">
-        <v>1.12106702818505e-05</v>
+        <v>1.121067028185039e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.928231993952055e-05</v>
+        <v>3.928231993952043e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001179691972618887</v>
+        <v>0.0001179691972618876</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002831740359223611</v>
+        <v>0.0002831740359223619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001696270356176103</v>
+        <v>0.0001696270356171056</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002698716403295494</v>
+        <v>0.0002698716403295492</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004504357304151745</v>
+        <v>0.0004504357304151717</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600481086711</v>
+        <v>0.0291060048108685</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2620763088575088</v>
+        <v>0.2620763088575091</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1650354498954149</v>
+        <v>0.165035449895415</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0754582083088931</v>
+        <v>0.07545820830889319</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008676015011131983</v>
+        <v>-0.008676015011132016</v>
       </c>
       <c r="H8" t="n">
-        <v>3.562394167423636e-06</v>
+        <v>3.562394167423464e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.183983614280502e-05</v>
+        <v>3.183983614280513e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.560562487960501e-05</v>
+        <v>8.560562487960755e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002684537004831265</v>
+        <v>0.0002684537004831272</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001495133400148695</v>
+        <v>0.0001495133400159496</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002632184485004554</v>
+        <v>0.0002632184485004551</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003504674230908813</v>
+        <v>0.0003504674230908825</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600489705359</v>
+        <v>0.0291060048970527</v>
       </c>
     </row>
     <row r="9">
@@ -1474,37 +1474,37 @@
         <v>0.4378111277657809</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1822659711988445</v>
+        <v>0.1822659711988444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1821547836721257</v>
+        <v>0.1821547836721258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04134214626745761</v>
+        <v>0.04134214626745768</v>
       </c>
       <c r="H9" t="n">
-        <v>8.798208131902848e-05</v>
+        <v>8.798208131902863e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001380141851365453</v>
+        <v>0.0001380141851365448</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004426989295353267</v>
+        <v>0.0004426989295353237</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003796246588119625</v>
+        <v>0.0003796246588119624</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003754309712549646</v>
+        <v>0.0003754309712545085</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003427765497631437</v>
+        <v>0.0003427765497631469</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001175695747841808</v>
+        <v>0.00117569574784181</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600350369036</v>
+        <v>0.02910600350369075</v>
       </c>
     </row>
     <row r="10">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3412637222584256</v>
+        <v>0.341263722258426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1735186361978786</v>
+        <v>0.1735186361978787</v>
       </c>
       <c r="F10" t="n">
         <v>0.1230752955770191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01355015218311549</v>
+        <v>0.01355015218311555</v>
       </c>
       <c r="H10" t="n">
-        <v>4.281361698979369e-05</v>
+        <v>4.281361698979371e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>8.429094510629887e-05</v>
+        <v>8.429094510629877e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000247151801561361</v>
+        <v>0.0002471518015613611</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003291111247146677</v>
+        <v>0.0003291111247146676</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002534848688861409</v>
+        <v>0.0002534848688860881</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003092144791355738</v>
+        <v>0.0003092144791355731</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007475671624110939</v>
+        <v>0.0007475671624110949</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600430160742</v>
+        <v>0.02910600430160787</v>
       </c>
     </row>
     <row r="11">
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2819651089329694</v>
+        <v>0.2819651089329697</v>
       </c>
       <c r="E11" t="n">
         <v>0.1682601739045025</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08674052130225883</v>
+        <v>0.0867405213022589</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.003602093331551</v>
+        <v>-0.00360209333155099</v>
       </c>
       <c r="H11" t="n">
-        <v>1.561661817671804e-05</v>
+        <v>1.56166181767182e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>4.624225401687266e-05</v>
+        <v>4.624225401687228e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001379871920300356</v>
+        <v>0.0001379871920300392</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002943872889499766</v>
+        <v>0.0002943872889499774</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001800216207148012</v>
+        <v>0.0001800216207148445</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002740818955873534</v>
+        <v>0.0002740818955873555</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005121653923313846</v>
+        <v>0.000512165392331434</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600479595188</v>
+        <v>0.02910600479595199</v>
       </c>
     </row>
   </sheetData>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.8318367627511341</v>
+        <v>-0.8318367627511335</v>
       </c>
       <c r="E2" t="n">
         <v>-1.546911021552864</v>
@@ -1774,61 +1774,61 @@
         <v>0.3361964245403627</v>
       </c>
       <c r="G2" t="n">
-        <v>2.965692463811938e-07</v>
+        <v>2.965692463811934e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.299317534700949e-06</v>
+        <v>8.299317534700954e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001241453184301911</v>
+        <v>0.0001241453184301914</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000412592677538388</v>
+        <v>0.0004125926775383875</v>
       </c>
       <c r="K2" t="n">
         <v>2.377451606960574e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.278859333192298e-05</v>
+        <v>1.278859333192103e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.531282222773754e-05</v>
+        <v>8.531282222773762e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008406755564804127</v>
+        <v>0.008406755564803779</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004329785081392348</v>
+        <v>0.004329785081392343</v>
       </c>
       <c r="P2" t="n">
-        <v>5.201863325538567e-05</v>
+        <v>5.201863325538565e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04431641876338697</v>
+        <v>0.04431641876338313</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003371153386280894</v>
+        <v>0.0003371153386280895</v>
       </c>
       <c r="S2" t="n">
-        <v>6.085770723093074e-06</v>
+        <v>6.085770723093071e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2289955955271886</v>
+        <v>0.2289955955271883</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04227130992846669</v>
+        <v>0.04227130992846666</v>
       </c>
       <c r="V2" t="n">
         <v>3.147626829962405e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004016718775058495</v>
+        <v>0.00040167187750585</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01485851061258492</v>
+        <v>0.01485851061258491</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03423216646391794</v>
+        <v>0.03423216646391795</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.8899286417722736</v>
+        <v>-0.8899286417722789</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.551698971083271</v>
+        <v>-1.55169897108327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3024108743409471</v>
+        <v>0.3024108743409485</v>
       </c>
       <c r="G3" t="n">
-        <v>2.913556405602291e-07</v>
+        <v>2.913556405602292e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.19244766206374e-06</v>
+        <v>8.192447662063776e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001182094654764929</v>
+        <v>0.0001182094654764926</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003790579604269342</v>
+        <v>0.000379057960426934</v>
       </c>
       <c r="K3" t="n">
-        <v>2.255464133251988e-05</v>
+        <v>2.255464133251992e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.560365380601449e-06</v>
+        <v>9.560365380602749e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.320443945428972e-05</v>
+        <v>7.320443945428969e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006668732196496181</v>
+        <v>0.006668732196508446</v>
       </c>
       <c r="O3" t="n">
         <v>0.004028407106369559</v>
@@ -1888,31 +1888,31 @@
         <v>4.461104723036827e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04229854053953782</v>
+        <v>0.04229854053953488</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000325574219348054</v>
+        <v>0.0003255742193480538</v>
       </c>
       <c r="S3" t="n">
-        <v>5.806137719731486e-06</v>
+        <v>5.806137719731462e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2175915407940366</v>
+        <v>0.2175915407940368</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04025218641642348</v>
+        <v>0.04025218641642343</v>
       </c>
       <c r="V3" t="n">
-        <v>3.068919424822648e-06</v>
+        <v>3.068919424822657e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003769658717695396</v>
+        <v>0.0003769658717695399</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01394968134156842</v>
+        <v>0.01394968134156848</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0332032270365067</v>
+        <v>0.03320322703650676</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9325568588032916</v>
+        <v>-0.9325568588032795</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.555551321266467</v>
+        <v>-1.55555132126647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2739584574408708</v>
+        <v>0.2739584574408707</v>
       </c>
       <c r="G4" t="n">
-        <v>2.891214402085847e-07</v>
+        <v>2.891214402085846e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.089359089440964e-06</v>
+        <v>8.089359089440943e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001136695147860584</v>
+        <v>0.0001136695147860582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00038187259259834</v>
+        <v>0.0003818725925983398</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208616895876115e-05</v>
+        <v>2.208616895876111e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.142570379069835e-05</v>
+        <v>1.142570379069837e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.406447584143261e-05</v>
+        <v>6.406447584143269e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007437704532451571</v>
+        <v>0.007437704532431035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003624892587084502</v>
+        <v>0.00362489258708451</v>
       </c>
       <c r="P4" t="n">
-        <v>3.895583381334161e-05</v>
+        <v>3.895583381334162e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04084272446110264</v>
+        <v>0.04084272446109416</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003068520323935346</v>
+        <v>0.0003068520323935877</v>
       </c>
       <c r="S4" t="n">
-        <v>5.703326879479336e-06</v>
+        <v>5.703326879479382e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.210036926796959</v>
+        <v>0.2100369267969593</v>
       </c>
       <c r="U4" t="n">
         <v>0.03954559184252743</v>
       </c>
       <c r="V4" t="n">
-        <v>3.043074396944945e-06</v>
+        <v>3.043074396944944e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003781714583220806</v>
+        <v>0.0003781714583220808</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01395357111282993</v>
+        <v>0.01395357111282986</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03226032871386401</v>
+        <v>0.03226032871386393</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9610042797343921</v>
+        <v>-0.961004279734393</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.558078749691933</v>
+        <v>-1.558078749691931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2686658744523964</v>
+        <v>0.2686658744523978</v>
       </c>
       <c r="G5" t="n">
-        <v>2.897866351763606e-07</v>
+        <v>2.897866351763594e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.952851542098832e-06</v>
+        <v>7.952851542098844e-06</v>
       </c>
       <c r="I5" t="n">
         <v>0.0001089211340744994</v>
@@ -2038,43 +2038,43 @@
         <v>0.0003773836952300434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.849084162415463e-05</v>
+        <v>1.849084162415461e-05</v>
       </c>
       <c r="L5" t="n">
         <v>1.576023537294646e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.752074266559439e-05</v>
+        <v>6.752074266559455e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009473451012544109</v>
+        <v>0.009473451012549487</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003178356408303753</v>
+        <v>0.00317835640830375</v>
       </c>
       <c r="P5" t="n">
-        <v>4.098098693924283e-05</v>
+        <v>4.098098693924285e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03825761146181197</v>
+        <v>0.03825761146180005</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002854582417799095</v>
+        <v>0.0002854582417799099</v>
       </c>
       <c r="S5" t="n">
-        <v>5.692182092243681e-06</v>
+        <v>5.692182092243654e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.190942715580153</v>
+        <v>0.1909427155801539</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03949088528806881</v>
+        <v>0.03949088528806886</v>
       </c>
       <c r="V5" t="n">
-        <v>2.888630117398988e-06</v>
+        <v>2.888630117398989e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003950802924558246</v>
+        <v>0.0003950802924558247</v>
       </c>
       <c r="X5" t="n">
         <v>0.01450133346268053</v>
@@ -2101,70 +2101,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.214345340757594</v>
+        <v>-1.21434534075758</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.581940595563529</v>
+        <v>-1.581940595563528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2172759522144011</v>
+        <v>0.2172759522144014</v>
       </c>
       <c r="G6" t="n">
-        <v>2.647205223344928e-07</v>
+        <v>2.647205223344917e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.033033267627473e-06</v>
+        <v>7.033033267627463e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.405339871544764e-05</v>
+        <v>6.405339871544769e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000232359027998093</v>
+        <v>0.0002323590279974462</v>
       </c>
       <c r="K6" t="n">
-        <v>9.590224339855894e-06</v>
+        <v>9.59022433985586e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.473351551477947e-06</v>
+        <v>4.473351551477939e-06</v>
       </c>
       <c r="M6" t="n">
         <v>3.184655774664003e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003582979316743277</v>
+        <v>0.003582979316755782</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001497757878139535</v>
+        <v>0.001497757878139534</v>
       </c>
       <c r="P6" t="n">
-        <v>2.009157345048726e-05</v>
+        <v>2.009157345048725e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01758459928196839</v>
+        <v>0.01758459928196327</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001284309419507246</v>
+        <v>0.0001284309419507245</v>
       </c>
       <c r="S6" t="n">
-        <v>4.008760422790605e-06</v>
+        <v>4.008760422790611e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06289437900603606</v>
+        <v>0.0628943790060358</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02789301190265926</v>
+        <v>0.02789301190265931</v>
       </c>
       <c r="V6" t="n">
         <v>2.420562301944111e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003170905511888872</v>
+        <v>0.0003170905511888873</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01153573242447717</v>
+        <v>0.01153573242447718</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02450914549601206</v>
+        <v>0.02450914549601211</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.410182621524585</v>
+        <v>-1.410182621524582</v>
       </c>
       <c r="E7" t="n">
         <v>-1.601206211225018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1547429780330178</v>
+        <v>0.154742978033018</v>
       </c>
       <c r="G7" t="n">
-        <v>2.446044256251515e-07</v>
+        <v>2.446044256251509e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442096151646407e-06</v>
+        <v>6.442096151646379e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770422375687518e-05</v>
+        <v>2.770422375687461e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001298426255663872</v>
+        <v>0.0001298426255663866</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.396929241751826e-06</v>
+        <v>-8.396929241751814e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>5.805497197919515e-07</v>
+        <v>5.805497197925326e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.000391007392921e-05</v>
+        <v>-2.000391007392924e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001268320539847134</v>
+        <v>0.001268320539838841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002331686864616773</v>
+        <v>0.000233168686461676</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.077758791439362e-05</v>
+        <v>-1.077758791439367e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003018109874445207</v>
+        <v>0.00301810987444831</v>
       </c>
       <c r="R7" t="n">
-        <v>5.34108839734073e-05</v>
+        <v>5.341088397340723e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.815905774000133e-06</v>
+        <v>2.815905774000105e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01811159063342173</v>
+        <v>-0.018111590633422</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0201451726724924</v>
+        <v>0.02014517267249236</v>
       </c>
       <c r="V7" t="n">
-        <v>1.625285506723564e-06</v>
+        <v>1.625285506723567e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002774825994218644</v>
+        <v>0.0002774825994218636</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009834654166229129</v>
+        <v>0.009834654166229121</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01943177570532376</v>
+        <v>0.01943177570532372</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.453464828470376</v>
+        <v>-1.453464828470397</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.606201264717674</v>
+        <v>-1.606201264717675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1400943034061174</v>
+        <v>0.1400943034061187</v>
       </c>
       <c r="G8" t="n">
-        <v>2.393217858839118e-07</v>
+        <v>2.393217858839132e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.335544213530667e-06</v>
+        <v>6.33554421353068e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.010386983685856e-05</v>
+        <v>2.010386983685912e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.458790381037149e-05</v>
+        <v>5.458790381070608e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.273154749541744e-05</v>
+        <v>-1.273154749541742e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.189015532872036e-07</v>
+        <v>-6.189015532872142e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.066748761499836e-05</v>
+        <v>-2.066748761499823e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005453538392290258</v>
+        <v>0.000545353839220499</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001999270889226515</v>
+        <v>0.0001999270889226496</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.130433784507029e-05</v>
+        <v>-1.130433784507027e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0001009093017669441</v>
+        <v>-0.000100909301747853</v>
       </c>
       <c r="R8" t="n">
-        <v>5.046903136687012e-05</v>
+        <v>5.04690313668701e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.523538981750777e-06</v>
+        <v>2.523538981750794e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.03419117807884192</v>
+        <v>-0.03419117807884224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01832117629705289</v>
+        <v>0.01832117629705288</v>
       </c>
       <c r="V8" t="n">
-        <v>1.472865921991581e-06</v>
+        <v>1.47286592199158e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002642465629666147</v>
+        <v>0.0002642465629666149</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009325281105489471</v>
+        <v>0.009325281105489433</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0181877960730185</v>
+        <v>0.01818779607301851</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2353,67 +2353,67 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9816773943303504</v>
+        <v>-0.9816773943303403</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.560477678769051</v>
+        <v>-1.560477678769054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2759700899639653</v>
+        <v>0.2759700899639649</v>
       </c>
       <c r="G9" t="n">
-        <v>2.837014222025333e-07</v>
+        <v>2.837014222025345e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.000478904578813e-06</v>
+        <v>8.000478904578947e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001039646830311864</v>
+        <v>0.0001039646830311858</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003206668189657246</v>
+        <v>0.0003206668189657443</v>
       </c>
       <c r="K9" t="n">
-        <v>1.725475435027212e-05</v>
+        <v>1.725475435027215e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.327382160729841e-06</v>
+        <v>8.32738216073829e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>5.250591226733452e-05</v>
+        <v>5.250591226733473e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005819705930074793</v>
+        <v>0.005819705930075656</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00374776932556763</v>
+        <v>0.003747769325567629</v>
       </c>
       <c r="P9" t="n">
-        <v>3.213528967834039e-05</v>
+        <v>3.213528967834054e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03583693923638698</v>
+        <v>0.03583693923636358</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002875038294114476</v>
+        <v>0.000287503829411448</v>
       </c>
       <c r="S9" t="n">
-        <v>5.343192153412972e-06</v>
+        <v>5.343192153412966e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1752259021330012</v>
+        <v>0.1752259021330017</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03703092045341563</v>
+        <v>0.03703092045341566</v>
       </c>
       <c r="V9" t="n">
-        <v>2.812444396054669e-06</v>
+        <v>2.81244439605467e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003599048957664521</v>
+        <v>0.000359904895766452</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01326305923251249</v>
+        <v>0.01326305923251248</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03070715431737227</v>
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.242785891600673</v>
+        <v>-1.242785891600679</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.583954092606448</v>
+        <v>-1.583954092606449</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2009807515308773</v>
+        <v>0.2009807515308784</v>
       </c>
       <c r="G10" t="n">
-        <v>2.606535231856346e-07</v>
+        <v>2.606535231856383e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.341437177856551e-06</v>
+        <v>7.341437177856542e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>5.804183610040383e-05</v>
+        <v>5.8041836100404e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001991641288363846</v>
+        <v>0.0001991641288364471</v>
       </c>
       <c r="K10" t="n">
-        <v>5.74827032645293e-06</v>
+        <v>5.748270326452932e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>4.373156858208395e-06</v>
+        <v>4.373156858208407e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.01949798951852e-05</v>
+        <v>-1.019497989518521e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003432318404490959</v>
+        <v>0.00343231840449264</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005593551573233541</v>
+        <v>0.0005593551573233538</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.042040348344032e-06</v>
+        <v>-5.042040348344049e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01626330145089593</v>
+        <v>0.01626330145089807</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001911896163490691</v>
+        <v>0.000191189616349069</v>
       </c>
       <c r="S10" t="n">
-        <v>3.880986824142086e-06</v>
+        <v>3.880986824142078e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05655559345463235</v>
+        <v>0.05655559345463265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02720475041928912</v>
+        <v>0.02720475041928908</v>
       </c>
       <c r="V10" t="n">
         <v>2.265845353073727e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003161481518067732</v>
+        <v>0.0003161481518067735</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0113753928393393</v>
+        <v>0.01137539283933926</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02402352640323894</v>
+        <v>0.02402352640323895</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2521,70 +2521,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.385688274388556</v>
+        <v>-1.385688274388545</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.597390680708501</v>
+        <v>-1.597390680708502</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1665538562409579</v>
+        <v>0.166553856240959</v>
       </c>
       <c r="G11" t="n">
-        <v>2.486819275140079e-07</v>
+        <v>2.486819275140103e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.490124512816031e-06</v>
+        <v>6.490124512816086e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240530691326464e-05</v>
+        <v>3.240530691326591e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001303519905024281</v>
+        <v>0.0001303519905026399</v>
       </c>
       <c r="K11" t="n">
-        <v>4.233469589935256e-06</v>
+        <v>4.233469589935388e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.852182648274243e-06</v>
+        <v>1.852182648276857e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.63575052564516e-05</v>
+        <v>-1.635750525645152e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001951223356248478</v>
+        <v>0.001951223356240344</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002094303248604139</v>
+        <v>0.0002094303248603959</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.524319044482572e-06</v>
+        <v>-8.524319044482251e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004286897569940568</v>
+        <v>0.004286897569943887</v>
       </c>
       <c r="R11" t="n">
-        <v>6.320468555721794e-05</v>
+        <v>6.320468555703445e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.004742308581565e-06</v>
+        <v>3.00474230858159e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01366391878408773</v>
+        <v>-0.01366391878408767</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02136100704048463</v>
+        <v>0.02136100704048477</v>
       </c>
       <c r="V11" t="n">
-        <v>2.170451989898054e-06</v>
+        <v>2.17045198989806e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.000289750174659091</v>
+        <v>0.0002897501746590912</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01030009914522407</v>
+        <v>0.010300099145224</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02019495089303859</v>
+        <v>0.02019495089303863</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.605280120019521</v>
+        <v>-0.6052801200195227</v>
       </c>
       <c r="E2" t="n">
         <v>-1.546911021552864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5627530673585389</v>
+        <v>0.5627530673585392</v>
       </c>
       <c r="G2" t="n">
-        <v>2.965692463811938e-07</v>
+        <v>2.965692463811934e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.299317534700949e-06</v>
+        <v>8.299317534700954e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001241453184301911</v>
+        <v>0.0001241453184301914</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000412592677538388</v>
+        <v>0.0004125926775383875</v>
       </c>
       <c r="K2" t="n">
         <v>2.377451606960574e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.278859333192298e-05</v>
+        <v>1.278859333192103e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.531282222773754e-05</v>
+        <v>8.531282222773762e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008406755564804127</v>
+        <v>0.008406755564803779</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004329785081392348</v>
+        <v>0.004329785081392343</v>
       </c>
       <c r="P2" t="n">
-        <v>5.201863325538567e-05</v>
+        <v>5.201863325538565e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04431641876338697</v>
+        <v>0.04431641876338313</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003371153386280894</v>
+        <v>0.0003371153386280895</v>
       </c>
       <c r="S2" t="n">
-        <v>6.085770723093074e-06</v>
+        <v>6.085770723093071e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2289955955271886</v>
+        <v>0.2289955955271883</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04227130992846669</v>
+        <v>0.04227130992846666</v>
       </c>
       <c r="V2" t="n">
         <v>3.147626829962405e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004016718775058495</v>
+        <v>0.00040167187750585</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01485851061258492</v>
+        <v>0.01485851061258491</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03423216646391794</v>
+        <v>0.03423216646391795</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.7225435171623522</v>
+        <v>-0.7225435171623505</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.551698971083271</v>
+        <v>-1.55169897108327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4697959990148232</v>
+        <v>0.4697959990148233</v>
       </c>
       <c r="G3" t="n">
-        <v>2.913556405602291e-07</v>
+        <v>2.913556405602292e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.19244766206374e-06</v>
+        <v>8.192447662063776e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001182094654764929</v>
+        <v>0.0001182094654764926</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003790579604269342</v>
+        <v>0.000379057960426934</v>
       </c>
       <c r="K3" t="n">
-        <v>2.255464133251988e-05</v>
+        <v>2.255464133251992e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.560365380601449e-06</v>
+        <v>9.560365380602749e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.320443945428972e-05</v>
+        <v>7.320443945428969e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006668732196496181</v>
+        <v>0.006668732196508446</v>
       </c>
       <c r="O3" t="n">
         <v>0.004028407106369559</v>
@@ -2869,31 +2869,31 @@
         <v>4.461104723036827e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04229854053953782</v>
+        <v>0.04229854053953488</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000325574219348054</v>
+        <v>0.0003255742193480538</v>
       </c>
       <c r="S3" t="n">
-        <v>5.806137719731486e-06</v>
+        <v>5.806137719731462e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2175915407940366</v>
+        <v>0.2175915407940368</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04025218641642348</v>
+        <v>0.04025218641642343</v>
       </c>
       <c r="V3" t="n">
-        <v>3.068919424822648e-06</v>
+        <v>3.068919424822657e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003769658717695396</v>
+        <v>0.0003769658717695399</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01394968134156842</v>
+        <v>0.01394968134156848</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0332032270365067</v>
+        <v>0.03320322703650676</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7960333563638701</v>
+        <v>-0.7960333563638774</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.555551321266467</v>
+        <v>-1.55555132126647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4104819599324452</v>
+        <v>0.4104819599324459</v>
       </c>
       <c r="G4" t="n">
-        <v>2.891214402085847e-07</v>
+        <v>2.891214402085846e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.089359089440964e-06</v>
+        <v>8.089359089440943e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001136695147860584</v>
+        <v>0.0001136695147860582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00038187259259834</v>
+        <v>0.0003818725925983398</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208616895876115e-05</v>
+        <v>2.208616895876111e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.142570379069835e-05</v>
+        <v>1.142570379069837e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.406447584143261e-05</v>
+        <v>6.406447584143269e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007437704532451571</v>
+        <v>0.007437704532431035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003624892587084502</v>
+        <v>0.00362489258708451</v>
       </c>
       <c r="P4" t="n">
-        <v>3.895583381334161e-05</v>
+        <v>3.895583381334162e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04084272446110264</v>
+        <v>0.04084272446109416</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003068520323935346</v>
+        <v>0.0003068520323935877</v>
       </c>
       <c r="S4" t="n">
-        <v>5.703326879479336e-06</v>
+        <v>5.703326879479382e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.210036926796959</v>
+        <v>0.2100369267969593</v>
       </c>
       <c r="U4" t="n">
         <v>0.03954559184252743</v>
       </c>
       <c r="V4" t="n">
-        <v>3.043074396944945e-06</v>
+        <v>3.043074396944944e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003781714583220806</v>
+        <v>0.0003781714583220808</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01395357111282993</v>
+        <v>0.01395357111282986</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03226032871386401</v>
+        <v>0.03226032871386393</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,19 +2998,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8401332055963089</v>
+        <v>-0.8401332055963011</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.558078749691933</v>
+        <v>-1.558078749691931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3895369486366646</v>
+        <v>0.3895369486366626</v>
       </c>
       <c r="G5" t="n">
-        <v>2.897866351763606e-07</v>
+        <v>2.897866351763594e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.952851542098832e-06</v>
+        <v>7.952851542098844e-06</v>
       </c>
       <c r="I5" t="n">
         <v>0.0001089211340744994</v>
@@ -3019,43 +3019,43 @@
         <v>0.0003773836952300434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.849084162415463e-05</v>
+        <v>1.849084162415461e-05</v>
       </c>
       <c r="L5" t="n">
         <v>1.576023537294646e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.752074266559439e-05</v>
+        <v>6.752074266559455e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009473451012544109</v>
+        <v>0.009473451012549487</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003178356408303753</v>
+        <v>0.00317835640830375</v>
       </c>
       <c r="P5" t="n">
-        <v>4.098098693924283e-05</v>
+        <v>4.098098693924285e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03825761146181197</v>
+        <v>0.03825761146180005</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002854582417799095</v>
+        <v>0.0002854582417799099</v>
       </c>
       <c r="S5" t="n">
-        <v>5.692182092243681e-06</v>
+        <v>5.692182092243654e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.190942715580153</v>
+        <v>0.1909427155801539</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03949088528806881</v>
+        <v>0.03949088528806886</v>
       </c>
       <c r="V5" t="n">
-        <v>2.888630117398988e-06</v>
+        <v>2.888630117398989e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003950802924558246</v>
+        <v>0.0003950802924558247</v>
       </c>
       <c r="X5" t="n">
         <v>0.01450133346268053</v>
@@ -3082,70 +3082,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.105000608734675</v>
+        <v>-1.105000608734664</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.581940595563529</v>
+        <v>-1.581940595563528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3266206842790855</v>
+        <v>0.3266206842790849</v>
       </c>
       <c r="G6" t="n">
-        <v>2.647205223344928e-07</v>
+        <v>2.647205223344917e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.033033267627473e-06</v>
+        <v>7.033033267627463e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.405339871544764e-05</v>
+        <v>6.405339871544769e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000232359027998093</v>
+        <v>0.0002323590279974462</v>
       </c>
       <c r="K6" t="n">
-        <v>9.590224339855894e-06</v>
+        <v>9.59022433985586e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.473351551477947e-06</v>
+        <v>4.473351551477939e-06</v>
       </c>
       <c r="M6" t="n">
         <v>3.184655774664003e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003582979316743277</v>
+        <v>0.003582979316755782</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001497757878139535</v>
+        <v>0.001497757878139534</v>
       </c>
       <c r="P6" t="n">
-        <v>2.009157345048726e-05</v>
+        <v>2.009157345048725e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01758459928196839</v>
+        <v>0.01758459928196327</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001284309419507246</v>
+        <v>0.0001284309419507245</v>
       </c>
       <c r="S6" t="n">
-        <v>4.008760422790605e-06</v>
+        <v>4.008760422790611e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06289437900603606</v>
+        <v>0.0628943790060358</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02789301190265926</v>
+        <v>0.02789301190265931</v>
       </c>
       <c r="V6" t="n">
         <v>2.420562301944111e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003170905511888872</v>
+        <v>0.0003170905511888873</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01153573242447717</v>
+        <v>0.01153573242447718</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02450914549601206</v>
+        <v>0.02450914549601211</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.347664511507221</v>
+        <v>-1.347664511507222</v>
       </c>
       <c r="E7" t="n">
         <v>-1.601206211225018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2172610880742639</v>
+        <v>0.217261088074264</v>
       </c>
       <c r="G7" t="n">
-        <v>2.446044256251515e-07</v>
+        <v>2.446044256251509e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442096151646407e-06</v>
+        <v>6.442096151646379e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.770422375687518e-05</v>
+        <v>2.770422375687461e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001298426255663872</v>
+        <v>0.0001298426255663866</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.396929241751826e-06</v>
+        <v>-8.396929241751814e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>5.805497197919515e-07</v>
+        <v>5.805497197925326e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.000391007392921e-05</v>
+        <v>-2.000391007392924e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001268320539847134</v>
+        <v>0.001268320539838841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002331686864616773</v>
+        <v>0.000233168686461676</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.077758791439362e-05</v>
+        <v>-1.077758791439367e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003018109874445207</v>
+        <v>0.00301810987444831</v>
       </c>
       <c r="R7" t="n">
-        <v>5.34108839734073e-05</v>
+        <v>5.341088397340723e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>2.815905774000133e-06</v>
+        <v>2.815905774000105e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01811159063342173</v>
+        <v>-0.018111590633422</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0201451726724924</v>
+        <v>0.02014517267249236</v>
       </c>
       <c r="V7" t="n">
-        <v>1.625285506723564e-06</v>
+        <v>1.625285506723567e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002774825994218644</v>
+        <v>0.0002774825994218636</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009834654166229129</v>
+        <v>0.009834654166229121</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01943177570532376</v>
+        <v>0.01943177570532372</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.399302573322059</v>
+        <v>-1.39930257332206</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.606201264717674</v>
+        <v>-1.606201264717675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1942565585751311</v>
+        <v>0.1942565585751329</v>
       </c>
       <c r="G8" t="n">
-        <v>2.393217858839118e-07</v>
+        <v>2.393217858839132e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.335544213530667e-06</v>
+        <v>6.33554421353068e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.010386983685856e-05</v>
+        <v>2.010386983685912e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.458790381037149e-05</v>
+        <v>5.458790381070608e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.273154749541744e-05</v>
+        <v>-1.273154749541742e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.189015532872036e-07</v>
+        <v>-6.189015532872142e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.066748761499836e-05</v>
+        <v>-2.066748761499823e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005453538392290258</v>
+        <v>0.000545353839220499</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0001999270889226515</v>
+        <v>0.0001999270889226496</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.130433784507029e-05</v>
+        <v>-1.130433784507027e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0001009093017669441</v>
+        <v>-0.000100909301747853</v>
       </c>
       <c r="R8" t="n">
-        <v>5.046903136687012e-05</v>
+        <v>5.04690313668701e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.523538981750777e-06</v>
+        <v>2.523538981750794e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.03419117807884192</v>
+        <v>-0.03419117807884224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01832117629705289</v>
+        <v>0.01832117629705288</v>
       </c>
       <c r="V8" t="n">
-        <v>1.472865921991581e-06</v>
+        <v>1.47286592199158e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002642465629666147</v>
+        <v>0.0002642465629666149</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009325281105489471</v>
+        <v>0.009325281105489433</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0181877960730185</v>
+        <v>0.01818779607301851</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3334,67 +3334,67 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8250054441436981</v>
+        <v>-0.8250054441436971</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.560477678769051</v>
+        <v>-1.560477678769054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4326420402104562</v>
+        <v>0.4326420402104573</v>
       </c>
       <c r="G9" t="n">
-        <v>2.837014222025333e-07</v>
+        <v>2.837014222025345e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.000478904578813e-06</v>
+        <v>8.000478904578947e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001039646830311864</v>
+        <v>0.0001039646830311858</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003206668189657246</v>
+        <v>0.0003206668189657443</v>
       </c>
       <c r="K9" t="n">
-        <v>1.725475435027212e-05</v>
+        <v>1.725475435027215e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.327382160729841e-06</v>
+        <v>8.32738216073829e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>5.250591226733452e-05</v>
+        <v>5.250591226733473e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005819705930074793</v>
+        <v>0.005819705930075656</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00374776932556763</v>
+        <v>0.003747769325567629</v>
       </c>
       <c r="P9" t="n">
-        <v>3.213528967834039e-05</v>
+        <v>3.213528967834054e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03583693923638698</v>
+        <v>0.03583693923636358</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002875038294114476</v>
+        <v>0.000287503829411448</v>
       </c>
       <c r="S9" t="n">
-        <v>5.343192153412972e-06</v>
+        <v>5.343192153412966e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1752259021330012</v>
+        <v>0.1752259021330017</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03703092045341563</v>
+        <v>0.03703092045341566</v>
       </c>
       <c r="V9" t="n">
-        <v>2.812444396054669e-06</v>
+        <v>2.81244439605467e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003599048957664521</v>
+        <v>0.000359904895766452</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01326305923251249</v>
+        <v>0.01326305923251248</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03070715431737227</v>
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.155371334932196</v>
+        <v>-1.155371334932202</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.583954092606448</v>
+        <v>-1.583954092606449</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2883953082327533</v>
+        <v>0.2883953082327514</v>
       </c>
       <c r="G10" t="n">
-        <v>2.606535231856346e-07</v>
+        <v>2.606535231856383e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.341437177856551e-06</v>
+        <v>7.341437177856542e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>5.804183610040383e-05</v>
+        <v>5.8041836100404e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001991641288363846</v>
+        <v>0.0001991641288364471</v>
       </c>
       <c r="K10" t="n">
-        <v>5.74827032645293e-06</v>
+        <v>5.748270326452932e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>4.373156858208395e-06</v>
+        <v>4.373156858208407e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.01949798951852e-05</v>
+        <v>-1.019497989518521e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003432318404490959</v>
+        <v>0.00343231840449264</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005593551573233541</v>
+        <v>0.0005593551573233538</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.042040348344032e-06</v>
+        <v>-5.042040348344049e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01626330145089593</v>
+        <v>0.01626330145089807</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001911896163490691</v>
+        <v>0.000191189616349069</v>
       </c>
       <c r="S10" t="n">
-        <v>3.880986824142086e-06</v>
+        <v>3.880986824142078e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05655559345463235</v>
+        <v>0.05655559345463265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02720475041928912</v>
+        <v>0.02720475041928908</v>
       </c>
       <c r="V10" t="n">
         <v>2.265845353073727e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003161481518067732</v>
+        <v>0.0003161481518067735</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0113753928393393</v>
+        <v>0.01137539283933926</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02402352640323894</v>
+        <v>0.02402352640323895</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.329995648248209</v>
+        <v>-1.329995648248205</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.597390680708501</v>
+        <v>-1.597390680708502</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2222464824025765</v>
+        <v>0.2222464824025761</v>
       </c>
       <c r="G11" t="n">
-        <v>2.486819275140079e-07</v>
+        <v>2.486819275140103e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.490124512816031e-06</v>
+        <v>6.490124512816086e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240530691326464e-05</v>
+        <v>3.240530691326591e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001303519905024281</v>
+        <v>0.0001303519905026399</v>
       </c>
       <c r="K11" t="n">
-        <v>4.233469589935256e-06</v>
+        <v>4.233469589935388e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.852182648274243e-06</v>
+        <v>1.852182648276857e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.63575052564516e-05</v>
+        <v>-1.635750525645152e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001951223356248478</v>
+        <v>0.001951223356240344</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0002094303248604139</v>
+        <v>0.0002094303248603959</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.524319044482572e-06</v>
+        <v>-8.524319044482251e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004286897569940568</v>
+        <v>0.004286897569943887</v>
       </c>
       <c r="R11" t="n">
-        <v>6.320468555721794e-05</v>
+        <v>6.320468555703445e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.004742308581565e-06</v>
+        <v>3.00474230858159e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01366391878408773</v>
+        <v>-0.01366391878408767</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02136100704048463</v>
+        <v>0.02136100704048477</v>
       </c>
       <c r="V11" t="n">
-        <v>2.170451989898054e-06</v>
+        <v>2.17045198989806e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.000289750174659091</v>
+        <v>0.0002897501746590912</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01030009914522407</v>
+        <v>0.010300099145224</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02019495089303859</v>
+        <v>0.02019495089303863</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
